--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260520_213136.xlsx
@@ -5632,7 +5632,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
